--- a/summary.xlsx
+++ b/summary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\ode-solvers-in-r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7368E608-5A56-4480-A9A6-63175F932F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D13FF92E-221B-41DA-910F-4CCCBE4DC4DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
   <si>
     <t>Package</t>
   </si>
@@ -57,9 +57,6 @@
     <t>lsoda, lsode, lsodes, lsodar, vode, daspk, radau</t>
   </si>
   <si>
-    <t>Yes (via LSODA)</t>
-  </si>
-  <si>
     <t>Yes</t>
   </si>
   <si>
@@ -81,13 +78,28 @@
     <t>DSL</t>
   </si>
   <si>
-    <t>Extra</t>
-  </si>
-  <si>
     <t>DAE (via daspk), DDE (via dede)</t>
   </si>
   <si>
     <t>Code-generated C + LSODA-based backend</t>
+  </si>
+  <si>
+    <t>mrgsolve</t>
+  </si>
+  <si>
+    <t>C++ translation of DLSODA</t>
+  </si>
+  <si>
+    <t>Macros</t>
+  </si>
+  <si>
+    <t>lsoda</t>
+  </si>
+  <si>
+    <t>Yes (via lsoda)</t>
+  </si>
+  <si>
+    <t>Extra methods</t>
   </si>
 </sst>
 </file>
@@ -420,11 +432,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="3"/>
-    <col min="2" max="2" width="21.21875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="23.33203125" style="3" customWidth="1"/>
     <col min="3" max="3" width="20.88671875" style="3" customWidth="1"/>
     <col min="4" max="4" width="14.21875" style="3" customWidth="1"/>
     <col min="5" max="5" width="12.109375" style="3" customWidth="1"/>
@@ -456,7 +468,7 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="44.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -470,42 +482,65 @@
         <v>9</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="H2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="D3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>17</v>
+      <c r="G4" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/summary.xlsx
+++ b/summary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\ode-solvers-in-r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D13FF92E-221B-41DA-910F-4CCCBE4DC4DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4882E33C-C4A0-4A85-859E-2FCC0BDE54C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="28">
   <si>
     <t>Package</t>
   </si>
@@ -100,6 +100,15 @@
   </si>
   <si>
     <t>Extra methods</t>
+  </si>
+  <si>
+    <t>dMod</t>
+  </si>
+  <si>
+    <t>Estimation, Sensitivity</t>
+  </si>
+  <si>
+    <t>API-based</t>
   </si>
 </sst>
 </file>
@@ -123,12 +132,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -143,7 +158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -152,6 +167,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -432,11 +448,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="3"/>
-    <col min="2" max="2" width="23.33203125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="25.77734375" style="3" customWidth="1"/>
     <col min="3" max="3" width="20.88671875" style="3" customWidth="1"/>
     <col min="4" max="4" width="14.21875" style="3" customWidth="1"/>
     <col min="5" max="5" width="12.109375" style="3" customWidth="1"/>
@@ -543,6 +559,29 @@
         <v>21</v>
       </c>
     </row>
+    <row r="5" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" t="s">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/summary.xlsx
+++ b/summary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\ode-solvers-in-r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4882E33C-C4A0-4A85-859E-2FCC0BDE54C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99DF1B78-7B5E-485F-9FE0-1FEBB52BE15C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="42">
   <si>
     <t>Package</t>
   </si>
@@ -109,6 +109,49 @@
   </si>
   <si>
     <t>API-based</t>
+  </si>
+  <si>
+    <t>pracma</t>
+  </si>
+  <si>
+    <t>Pure R</t>
+  </si>
+  <si>
+    <t>RK4, RK45</t>
+  </si>
+  <si>
+    <t>Νο</t>
+  </si>
+  <si>
+    <t>R func</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t>Provides a large number of functions from numerical analysis and linear algebra, numerical optimization, differential equations, time series, plus some well-known special mathematical functions. Uses 'MATLAB' function names where appropriate to simplify porting.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The framework provides functions to generate ODEs of reaction networks, parameter transformations, observation functions, residual functions, etc. The framework follows the paradigm that derivative information should be used for optimization whenever possible. Therefore, all major functions produce and can handle expressions for symbolic derivatives. The methods used in dMod were published in Kaschek et al, 2019, &lt;doi:10.18637/jss.v088.i10&gt;.
+</t>
+  </si>
+  <si>
+    <t>Fast simulation from ordinary differential equation (ODE) based models typically employed in quantitative pharmacology and systems biology.</t>
+  </si>
+  <si>
+    <t>Facilities for running simulations from ordinary differential equation ('ODE') models, such as pharmacometrics and other compartmental models. A compilation manager translates the ODE model into C, compiles it, and dynamically loads the object code into R for improved computational efficiency. An event table object facilitates the specification of complex dosing regimens (optional) and sampling schedules. NB: The use of this package requires both C and Fortran compilers, for details on their use with R please see Section 6.3, Appendix A, and Appendix D in the "R Administration and Installation" manual. Also the code is mostly released under GPL. The 'VODE' and 'LSODA' are in the public domain. The information is available in the inst/COPYRIGHTS.</t>
+  </si>
+  <si>
+    <t>Functions that solve initial value problems of a system of first-order ordinary differential equations ('ODE'), of partial differential equations ('PDE'), of differential algebraic equations ('DAE'), and of delay differential equations. The functions provide an interface to the FORTRAN functions 'lsoda', 'lsodar', 'lsode', 'lsodes' of the 'ODEPACK' collection, to the FORTRAN functions 'dvode', 'zvode' and 'daspk' and a C-implementation of solvers of the 'Runge-Kutta' family with fixed or variable time steps. The package contains routines designed for solving 'ODEs' resulting from 1-D, 2-D and 3-D partial differential equations ('PDE') that have been converted to 'ODEs' by numerical differencing.</t>
+  </si>
+  <si>
+    <t>odin</t>
+  </si>
+  <si>
+    <t>Generate systems of ordinary differential equations (ODE) and integrate them, using a domain specific language (DSL). The DSL uses R's syntax, but compiles to C in order to efficiently solve the system. A solver is not provided, but instead interfaces to the packages 'deSolve' and 'dde' are generated. With these, while solving the differential equations, no allocations are done and the calculations remain entirely in compiled code. Alternatively, a model can be transpiled to R for use in contexts where a C compiler is not present. After compilation, models can be inspected to return information about parameters and outputs, or intermediate values after calculations. 'odin' is not targeted at any particular domain and is suitable for any system that can be expressed primarily as mathematical expressions. Additional support is provided for working with delays (delay differential equations, DDE), using interpolated functions during interpolation, and for integrating quantities that represent arrays.</t>
+  </si>
+  <si>
+    <t>DDE</t>
   </si>
 </sst>
 </file>
@@ -132,7 +175,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -142,6 +185,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -158,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -167,7 +216,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -448,20 +502,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="3"/>
     <col min="2" max="2" width="25.77734375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="20.88671875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="16.88671875" style="3" customWidth="1"/>
     <col min="4" max="4" width="14.21875" style="3" customWidth="1"/>
     <col min="5" max="5" width="12.109375" style="3" customWidth="1"/>
     <col min="6" max="6" width="17.21875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="23.33203125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="10.77734375" customWidth="1"/>
+    <col min="7" max="7" width="16.44140625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="10.77734375" style="3" customWidth="1"/>
+    <col min="9" max="9" width="81.44140625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -483,11 +538,14 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>24</v>
       </c>
+      <c r="I1" s="2" t="s">
+        <v>33</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" ht="44.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
@@ -497,23 +555,26 @@
       <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="5" t="s">
         <v>11</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="I2" s="3" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="3" spans="1:8" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="102.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>13</v>
       </c>
@@ -523,10 +584,10 @@
       <c r="C3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="5" t="s">
         <v>10</v>
       </c>
       <c r="F3" s="3" t="s">
@@ -535,21 +596,24 @@
       <c r="G3" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="I3" s="3" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="4" spans="1:8" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="5" t="s">
         <v>10</v>
       </c>
       <c r="F4" s="3" t="s">
@@ -558,15 +622,18 @@
       <c r="G4" s="3" t="s">
         <v>21</v>
       </c>
+      <c r="I4" s="3" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="5" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>25</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="5" t="s">
         <v>10</v>
       </c>
       <c r="E5" s="3" t="s">
@@ -575,11 +642,66 @@
       <c r="F5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="3" t="s">
         <v>26</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/summary.xlsx
+++ b/summary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\ode-solvers-in-r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99DF1B78-7B5E-485F-9FE0-1FEBB52BE15C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58EC24AF-B08F-4331-88FA-21EC5E537B6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="56">
   <si>
     <t>Package</t>
   </si>
@@ -78,9 +78,6 @@
     <t>DSL</t>
   </si>
   <si>
-    <t>DAE (via daspk), DDE (via dede)</t>
-  </si>
-  <si>
     <t>Code-generated C + LSODA-based backend</t>
   </si>
   <si>
@@ -90,9 +87,6 @@
     <t>C++ translation of DLSODA</t>
   </si>
   <si>
-    <t>Macros</t>
-  </si>
-  <si>
     <t>lsoda</t>
   </si>
   <si>
@@ -108,9 +102,6 @@
     <t>Estimation, Sensitivity</t>
   </si>
   <si>
-    <t>API-based</t>
-  </si>
-  <si>
     <t>pracma</t>
   </si>
   <si>
@@ -124,9 +115,6 @@
   </si>
   <si>
     <t>R func</t>
-  </si>
-  <si>
-    <t>Comments</t>
   </si>
   <si>
     <t>Provides a large number of functions from numerical analysis and linear algebra, numerical optimization, differential equations, time series, plus some well-known special mathematical functions. Uses 'MATLAB' function names where appropriate to simplify porting.</t>
@@ -152,13 +140,67 @@
   </si>
   <si>
     <t>DDE</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Just a connector from DSL to deSolve</t>
+  </si>
+  <si>
+    <t>PKPDsim</t>
+  </si>
+  <si>
+    <t>Simulate dose regimens for pharmacokinetic-pharmacodynamic (PK-PD) models described by differential equation (DE) systems. Simulation using ADVAN-style analytical equations is also supported</t>
+  </si>
+  <si>
+    <t>Boost::odeint (C++)</t>
+  </si>
+  <si>
+    <t>Adaptive RK (Cash–Karp 5(4)) (RKCK54)</t>
+  </si>
+  <si>
+    <t>DAE</t>
+  </si>
+  <si>
+    <t>Yes (via dede)</t>
+  </si>
+  <si>
+    <t>Yes (via daspk)</t>
+  </si>
+  <si>
+    <t>DSL (C++ like)</t>
+  </si>
+  <si>
+    <t>DSL (R like)</t>
+  </si>
+  <si>
+    <t>Model execution</t>
+  </si>
+  <si>
+    <t>Interpreted / Compiled</t>
+  </si>
+  <si>
+    <t>Compiled</t>
+  </si>
+  <si>
+    <t>Interpreted</t>
+  </si>
+  <si>
+    <t>Black box solver, cannot change method or solver parameters https://github.com/boostorg/odeint</t>
+  </si>
+  <si>
+    <t>DSL(cOde), API-based</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -169,7 +211,12 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -207,20 +254,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -502,50 +553,66 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="3"/>
     <col min="2" max="2" width="25.77734375" style="3" customWidth="1"/>
     <col min="3" max="3" width="16.88671875" style="3" customWidth="1"/>
     <col min="4" max="4" width="14.21875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="12.109375" style="3" customWidth="1"/>
-    <col min="6" max="6" width="17.21875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="16.44140625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="10.77734375" style="3" customWidth="1"/>
-    <col min="9" max="9" width="81.44140625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="15.88671875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="12.109375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="17.21875" style="3" customWidth="1"/>
+    <col min="8" max="8" width="16.44140625" style="3" customWidth="1"/>
+    <col min="9" max="10" width="9.33203125" style="3" customWidth="1"/>
+    <col min="11" max="11" width="10.77734375" style="3" customWidth="1"/>
+    <col min="12" max="12" width="81.44140625" style="3" customWidth="1"/>
+    <col min="13" max="13" width="17" style="5" customWidth="1"/>
+    <col min="14" max="16384" width="8.88671875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:13" s="2" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>33</v>
+      <c r="I1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
@@ -555,153 +622,209 @@
       <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" s="5" t="s">
+      <c r="D2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="I2" s="3" t="s">
-        <v>38</v>
+        <v>47</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="102.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" ht="102.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>37</v>
+      <c r="L3" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>36</v>
+      <c r="H4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="D6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" ht="72" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>40</v>
+      <c r="L8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/summary.xlsx
+++ b/summary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\ode-solvers-in-r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58EC24AF-B08F-4331-88FA-21EC5E537B6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4FF0F94-094A-4C9A-B9D9-0EFC48B86819}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="58">
   <si>
     <t>Package</t>
   </si>
@@ -51,12 +51,6 @@
     <t>deSolve</t>
   </si>
   <si>
-    <t>ODEPACK + DASPK (FORTRAN)</t>
-  </si>
-  <si>
-    <t>lsoda, lsode, lsodes, lsodar, vode, daspk, radau</t>
-  </si>
-  <si>
     <t>Yes</t>
   </si>
   <si>
@@ -78,18 +72,9 @@
     <t>DSL</t>
   </si>
   <si>
-    <t>Code-generated C + LSODA-based backend</t>
-  </si>
-  <si>
     <t>mrgsolve</t>
   </si>
   <si>
-    <t>C++ translation of DLSODA</t>
-  </si>
-  <si>
-    <t>lsoda</t>
-  </si>
-  <si>
     <t>Yes (via lsoda)</t>
   </si>
   <si>
@@ -106,9 +91,6 @@
   </si>
   <si>
     <t>Pure R</t>
-  </si>
-  <si>
-    <t>RK4, RK45</t>
   </si>
   <si>
     <t>Νο</t>
@@ -157,12 +139,6 @@
     <t>Simulate dose regimens for pharmacokinetic-pharmacodynamic (PK-PD) models described by differential equation (DE) systems. Simulation using ADVAN-style analytical equations is also supported</t>
   </si>
   <si>
-    <t>Boost::odeint (C++)</t>
-  </si>
-  <si>
-    <t>Adaptive RK (Cash–Karp 5(4)) (RKCK54)</t>
-  </si>
-  <si>
     <t>DAE</t>
   </si>
   <si>
@@ -190,17 +166,47 @@
     <t>Interpreted</t>
   </si>
   <si>
-    <t>Black box solver, cannot change method or solver parameters https://github.com/boostorg/odeint</t>
-  </si>
-  <si>
     <t>DSL(cOde), API-based</t>
+  </si>
+  <si>
+    <t>ode23, ode23s, ode45, ode78</t>
+  </si>
+  <si>
+    <t>Yes (via ode23s)</t>
+  </si>
+  <si>
+    <t>lsoda, lsode, lsodes, lsodar, vode, daspk, bdf, adams, impAdams, radau, euler, rk4, ode23, ode45,  etc.</t>
+  </si>
+  <si>
+    <t>Adaptive RK (RKCK54)</t>
+  </si>
+  <si>
+    <t>LSODA</t>
+  </si>
+  <si>
+    <t>Ref</t>
+  </si>
+  <si>
+    <t>ODEPACK (http://www.netlib.org/odepack/); DASPK (http://www.netlib.org/ode/) (in FORTRAN)</t>
+  </si>
+  <si>
+    <t>LIBLSODA (https://github.com/sdwfrost/liblsoda) + ported and original algorithms  (in C)</t>
+  </si>
+  <si>
+    <t>DLSODA (http://www.netlib.org/odepack/) (translated to C++)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black box solver, cannot change method or solver parameters </t>
+  </si>
+  <si>
+    <t>Boost::odeint (https://github.com/boostorg/odeint) (C++)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -221,6 +227,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -231,13 +245,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -251,10 +265,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -263,18 +278,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -553,25 +572,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="3"/>
-    <col min="2" max="2" width="25.77734375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="16.88671875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="14.21875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="15.88671875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="12.109375" style="3" customWidth="1"/>
-    <col min="7" max="7" width="17.21875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="16.44140625" style="3" customWidth="1"/>
-    <col min="9" max="10" width="9.33203125" style="3" customWidth="1"/>
-    <col min="11" max="11" width="10.77734375" style="3" customWidth="1"/>
-    <col min="12" max="12" width="81.44140625" style="3" customWidth="1"/>
-    <col min="13" max="13" width="17" style="5" customWidth="1"/>
-    <col min="14" max="16384" width="8.88671875" style="5"/>
+    <col min="2" max="3" width="25.77734375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="16.88671875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="14.21875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="15.88671875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="12.109375" style="3" customWidth="1"/>
+    <col min="8" max="8" width="17.21875" style="3" customWidth="1"/>
+    <col min="9" max="9" width="16.44140625" style="3" customWidth="1"/>
+    <col min="10" max="11" width="9.33203125" style="3" customWidth="1"/>
+    <col min="12" max="12" width="10.77734375" style="3" customWidth="1"/>
+    <col min="13" max="13" width="81.44140625" style="3" customWidth="1"/>
+    <col min="14" max="14" width="17" style="5" customWidth="1"/>
+    <col min="15" max="16384" width="8.88671875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="2" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" s="2" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -579,252 +598,258 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="F1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>45</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>37</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>39</v>
+        <v>17</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="8"/>
+      <c r="D2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="H2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="I2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="102.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="7"/>
+      <c r="E5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="L2" s="3" t="s">
+      <c r="E6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="E7" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N7" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="102.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+    <row r="8" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="I8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="L7" s="3" t="s">
+      <c r="M8" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="M7" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M8" s="5" t="s">
-        <v>54</v>
+      <c r="N8" s="5" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
